--- a/VerveStacks_TJK_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{914E8129-7848-4360-A080-F4EE4172D5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44FE02BA-E635-4D75-B1A9-851C9135F85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1260,7 +1260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28B72FF-7641-4DCE-A113-27212E301B00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{918BD40B-FB24-4904-BC2C-1FA74CDD3DC9}">
   <dimension ref="B2:AE59"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_TJK_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44FE02BA-E635-4D75-B1A9-851C9135F85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD74F51E-FE96-42E6-97C3-ED2C0A1C8D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1260,7 +1260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{918BD40B-FB24-4904-BC2C-1FA74CDD3DC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F4B0572-AA55-490F-A234-BDBC8CAA9024}">
   <dimension ref="B2:AE59"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_TJK_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD74F51E-FE96-42E6-97C3-ED2C0A1C8D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CF34307-6161-49F0-A9C5-AF581045ABE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1260,7 +1260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F4B0572-AA55-490F-A234-BDBC8CAA9024}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08F9759B-ACE2-4725-85FC-5F715BCA06AA}">
   <dimension ref="B2:AE59"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_TJK_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_TJK_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CF34307-6161-49F0-A9C5-AF581045ABE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F16D8C0-734B-4FF7-9C08-D9972718632C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1260,7 +1260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08F9759B-ACE2-4725-85FC-5F715BCA06AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02BF511-169B-4F03-B7B7-F9476F6720A0}">
   <dimension ref="B2:AE59"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
